--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikram41.kumar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikram41.kumar\OneDrive - Reliance Corporate IT Park Limited\Desktop\Data visualisation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CA95B92-F0B0-439A-94B3-B13FB28136BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="14_{F105B635-D779-4A62-9132-D6BD71D86E55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{CDAE1873-3863-463F-AE70-53D7C7263288}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="2" xr2:uid="{DF76643F-7F1E-4CB3-A76C-FE88BEEB8FCD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="4" xr2:uid="{DF76643F-7F1E-4CB3-A76C-FE88BEEB8FCD}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7353" uniqueCount="1685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7423" uniqueCount="1685">
   <si>
     <t>QA Game Count</t>
   </si>
@@ -5473,7 +5473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5788,6 +5788,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6114,7 +6124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA7A9DA-BB77-472E-AD3D-F1EEE7FA09E2}">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="55" customWidth="1"/>
@@ -9829,6 +9839,330 @@
       </c>
       <c r="F188" s="2" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="128">
+        <v>188</v>
+      </c>
+      <c r="B189" s="18" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C189" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D189" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E189" s="129"/>
+      <c r="F189" s="130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="131">
+        <v>189</v>
+      </c>
+      <c r="B190" s="32" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C190" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D190" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E190" s="132"/>
+      <c r="F190" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="131">
+        <v>190</v>
+      </c>
+      <c r="B191" s="32" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C191" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D191" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E191" s="132"/>
+      <c r="F191" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" s="131">
+        <v>191</v>
+      </c>
+      <c r="B192" s="32" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C192" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D192" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E192" s="132"/>
+      <c r="F192" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" s="131">
+        <v>192</v>
+      </c>
+      <c r="B193" s="32" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C193" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E193" s="132"/>
+      <c r="F193" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="131">
+        <v>193</v>
+      </c>
+      <c r="B194" s="32" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C194" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E194" s="132"/>
+      <c r="F194" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="131">
+        <v>194</v>
+      </c>
+      <c r="B195" s="32" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C195" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D195" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E195" s="132"/>
+      <c r="F195" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="131">
+        <v>195</v>
+      </c>
+      <c r="B196" s="32" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C196" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D196" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E196" s="132"/>
+      <c r="F196" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="131">
+        <v>196</v>
+      </c>
+      <c r="B197" s="32" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C197" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D197" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E197" s="132"/>
+      <c r="F197" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="131">
+        <v>197</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C198" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D198" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E198" s="132"/>
+      <c r="F198" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="131">
+        <v>198</v>
+      </c>
+      <c r="B199" s="32" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C199" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D199" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E199" s="132"/>
+      <c r="F199" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="131">
+        <v>199</v>
+      </c>
+      <c r="B200" s="32" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C200" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D200" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E200" s="132"/>
+      <c r="F200" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="131">
+        <v>200</v>
+      </c>
+      <c r="B201" s="32" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C201" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D201" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E201" s="132"/>
+      <c r="F201" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="131">
+        <v>201</v>
+      </c>
+      <c r="B202" s="32" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C202" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D202" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E202" s="132"/>
+      <c r="F202" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="131">
+        <v>202</v>
+      </c>
+      <c r="B203" s="32" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C203" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E203" s="132"/>
+      <c r="F203" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="131">
+        <v>203</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C204" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E204" s="132"/>
+      <c r="F204" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="131">
+        <v>204</v>
+      </c>
+      <c r="B205" s="32" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C205" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D205" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E205" s="132"/>
+      <c r="F205" s="133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="131">
+        <v>205</v>
+      </c>
+      <c r="B206" s="32" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C206" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D206" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E206" s="132"/>
+      <c r="F206" s="133" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -37604,7 +37938,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF301802-3853-45FA-B67C-3ED0CBA93388}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -38507,7 +38841,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="57" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="C82" t="s">
         <v>7</v>
@@ -38518,7 +38852,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="57" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C83" t="s">
         <v>7</v>
@@ -38528,8 +38862,8 @@
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="57" t="s">
-        <v>1671</v>
+      <c r="B84" s="78" t="s">
+        <v>1672</v>
       </c>
       <c r="C84" t="s">
         <v>7</v>
@@ -38540,7 +38874,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="78" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="C85" t="s">
         <v>7</v>
@@ -38551,7 +38885,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="78" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C86" t="s">
         <v>7</v>
@@ -38562,7 +38896,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="78" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="C87" t="s">
         <v>7</v>
@@ -38573,7 +38907,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="78" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="C88" t="s">
         <v>7</v>
@@ -38584,7 +38918,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="78" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C89" t="s">
         <v>7</v>
@@ -38595,20 +38929,9 @@
         <v>89</v>
       </c>
       <c r="B90" s="78" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="C90" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" s="78" t="s">
-        <v>1678</v>
-      </c>
-      <c r="C91" t="s">
         <v>7</v>
       </c>
     </row>
@@ -38618,23 +38941,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010093D215910041EE46A205026926E3B56E" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d0787ea4e0bf2a0aee8f9298c22e065a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xmlns:ns4="376f05cc-017a-41da-a922-00fd3d15c307" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c55527503b43b5b1a5ab13dc735f56b7" ns3:_="" ns4:_="">
     <xsd:import namespace="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
@@ -38867,32 +39173,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E805F6-E3B0-439E-ABEC-4D5783707228}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="376f05cc-017a-41da-a922-00fd3d15c307"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B27006A-6696-4AD1-BBDC-E624CE86121C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48FB8BFB-5F9A-406C-9025-A3ADAD915C21}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38909,4 +39207,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B27006A-6696-4AD1-BBDC-E624CE86121C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E805F6-E3B0-439E-ABEC-4D5783707228}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="376f05cc-017a-41da-a922-00fd3d15c307"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>